--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128218220</v>
+        <v>128216979</v>
       </c>
       <c r="B3" t="n">
         <v>57669</v>
@@ -815,14 +815,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>340367</v>
+        <v>340348</v>
       </c>
       <c r="R3" t="n">
-        <v>6435590</v>
+        <v>6435622</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128216979</v>
+        <v>128218220</v>
       </c>
       <c r="B4" t="n">
         <v>57669</v>
@@ -931,10 +927,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>340348</v>
+        <v>340367</v>
       </c>
       <c r="R4" t="n">
-        <v>6435622</v>
+        <v>6435590</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1130,7 +1130,7 @@
         <v>128217724</v>
       </c>
       <c r="B6" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128222392</v>
       </c>
       <c r="B9" t="n">
-        <v>97095</v>
+        <v>97096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128218812</v>
       </c>
       <c r="B10" t="n">
-        <v>97337</v>
+        <v>97338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>128217724</v>
       </c>
       <c r="B6" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128222392</v>
       </c>
       <c r="B9" t="n">
-        <v>97096</v>
+        <v>97097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128218812</v>
       </c>
       <c r="B10" t="n">
-        <v>97338</v>
+        <v>97339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,6 +1681,1754 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128474972</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>340344</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6435655</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vid basen av död tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128474772</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56248</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>340422</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6435610</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128475015</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>340334</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6435676</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På låga vid bergimpediment</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128475036</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>340341</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6435692</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På låga</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128475088</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>340470</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6435648</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128474395</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>340271</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6435541</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128474510</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>340360</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6435545</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spår vid basen av död stående tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128474743</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95720</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>340316</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6435655</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>noterad</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128474957</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>340352</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6435653</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På låga</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128474296</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97355</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>340336</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6435460</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växte i ett fuktdråg</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128475218</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>340418</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6435698</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Vid basen av död tall.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128475242</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>340367</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6435710</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Vid basen av död tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128474420</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>340228</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6435559</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska spår vid basen av mindre döende ek</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128474707</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>340311</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6435634</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska spår vid basen av död tallraka</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128474935</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>340377</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6435663</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Medelfärska spår av födosökande spillkråka vid basen av död tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128474886</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hylta Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>340394</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6435660</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spår vid basen av död tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128216776</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128216979</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128218220</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128219094</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128217724</v>
       </c>
       <c r="B6" t="n">
-        <v>96072</v>
+        <v>96080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128217219</v>
       </c>
       <c r="B7" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128218572</v>
       </c>
       <c r="B8" t="n">
-        <v>58349</v>
+        <v>58350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128222392</v>
       </c>
       <c r="B9" t="n">
-        <v>97097</v>
+        <v>97105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128218812</v>
       </c>
       <c r="B10" t="n">
-        <v>97339</v>
+        <v>97347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128475015</v>
+        <v>128475036</v>
       </c>
       <c r="B13" t="n">
         <v>57670</v>
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>340334</v>
+        <v>340341</v>
       </c>
       <c r="R13" t="n">
-        <v>6435676</v>
+        <v>6435692</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På låga vid bergimpediment</t>
+          <t>På låga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128475036</v>
+        <v>128475015</v>
       </c>
       <c r="B14" t="n">
         <v>57670</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>340341</v>
+        <v>340334</v>
       </c>
       <c r="R14" t="n">
-        <v>6435692</v>
+        <v>6435676</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På låga</t>
+          <t>På låga vid bergimpediment</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128474395</v>
+        <v>128474510</v>
       </c>
       <c r="B16" t="n">
         <v>57670</v>
@@ -2265,7 +2265,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>340271</v>
+        <v>340360</v>
       </c>
       <c r="R16" t="n">
-        <v>6435541</v>
+        <v>6435545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,6 +2311,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spår vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,7 +2342,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128474510</v>
+        <v>128474395</v>
       </c>
       <c r="B17" t="n">
         <v>57670</v>
@@ -2370,7 +2375,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2380,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>340360</v>
+        <v>340271</v>
       </c>
       <c r="R17" t="n">
-        <v>6435545</v>
+        <v>6435541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,11 +2421,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spår vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128216776</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128216979</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128218220</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128219094</v>
       </c>
       <c r="B5" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128217724</v>
       </c>
       <c r="B6" t="n">
-        <v>96080</v>
+        <v>96173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128217219</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128218572</v>
       </c>
       <c r="B8" t="n">
-        <v>58350</v>
+        <v>58362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128222392</v>
       </c>
       <c r="B9" t="n">
-        <v>97105</v>
+        <v>97198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128218812</v>
       </c>
       <c r="B10" t="n">
-        <v>97347</v>
+        <v>97440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>128474972</v>
       </c>
       <c r="B11" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>128474772</v>
       </c>
       <c r="B12" t="n">
-        <v>56248</v>
+        <v>56260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128475036</v>
       </c>
       <c r="B13" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128475015</v>
       </c>
       <c r="B14" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128475088</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128474510</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128474395</v>
       </c>
       <c r="B17" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95720</v>
+        <v>95813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128474957</v>
       </c>
       <c r="B19" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>128475218</v>
       </c>
       <c r="B21" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128475242</v>
       </c>
       <c r="B22" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128474420</v>
       </c>
       <c r="B23" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>128474707</v>
       </c>
       <c r="B24" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128474935</v>
       </c>
       <c r="B25" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128474886</v>
       </c>
       <c r="B26" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>128474972</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>128474772</v>
       </c>
       <c r="B12" t="n">
-        <v>56260</v>
+        <v>56264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128475036</v>
       </c>
       <c r="B13" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128475015</v>
       </c>
       <c r="B14" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128475088</v>
       </c>
       <c r="B15" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128474510</v>
       </c>
       <c r="B16" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128474395</v>
       </c>
       <c r="B17" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95813</v>
+        <v>95819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128474957</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>128475218</v>
       </c>
       <c r="B21" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128475242</v>
       </c>
       <c r="B22" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128474420</v>
       </c>
       <c r="B23" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>128474707</v>
       </c>
       <c r="B24" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128474935</v>
       </c>
       <c r="B25" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128474886</v>
       </c>
       <c r="B26" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128216776</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128216979</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128218220</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128219094</v>
       </c>
       <c r="B5" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128217724</v>
       </c>
       <c r="B6" t="n">
-        <v>96173</v>
+        <v>96185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128217219</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128218572</v>
       </c>
       <c r="B8" t="n">
-        <v>58362</v>
+        <v>58366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128222392</v>
       </c>
       <c r="B9" t="n">
-        <v>97198</v>
+        <v>97210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128218812</v>
       </c>
       <c r="B10" t="n">
-        <v>97440</v>
+        <v>97452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95819</v>
+        <v>95825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>128217724</v>
       </c>
       <c r="B6" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128222392</v>
       </c>
       <c r="B9" t="n">
-        <v>97210</v>
+        <v>97212</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128218812</v>
       </c>
       <c r="B10" t="n">
-        <v>97452</v>
+        <v>97454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95825</v>
+        <v>95827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>128217724</v>
       </c>
       <c r="B6" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128222392</v>
       </c>
       <c r="B9" t="n">
-        <v>97212</v>
+        <v>97213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128218812</v>
       </c>
       <c r="B10" t="n">
-        <v>97454</v>
+        <v>97455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95827</v>
+        <v>95828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128216776</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128216979</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128218220</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128219094</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128217724</v>
       </c>
       <c r="B6" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128217219</v>
       </c>
       <c r="B7" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128218572</v>
       </c>
       <c r="B8" t="n">
-        <v>58366</v>
+        <v>58393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128222392</v>
       </c>
       <c r="B9" t="n">
-        <v>97213</v>
+        <v>97240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128218812</v>
       </c>
       <c r="B10" t="n">
-        <v>97455</v>
+        <v>97482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>128474972</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>128474772</v>
       </c>
       <c r="B12" t="n">
-        <v>56264</v>
+        <v>56291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128475036</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128475015</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128475088</v>
       </c>
       <c r="B15" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128474510</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128474395</v>
       </c>
       <c r="B17" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95828</v>
+        <v>95855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128474957</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>128475218</v>
       </c>
       <c r="B21" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128475242</v>
       </c>
       <c r="B22" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128474420</v>
       </c>
       <c r="B23" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>128474707</v>
       </c>
       <c r="B24" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128474935</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128474886</v>
       </c>
       <c r="B26" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95855</v>
+        <v>95868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>128474972</v>
       </c>
       <c r="B11" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>128474772</v>
       </c>
       <c r="B12" t="n">
-        <v>56291</v>
+        <v>56294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128475036</v>
       </c>
       <c r="B13" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128475015</v>
       </c>
       <c r="B14" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128475088</v>
       </c>
       <c r="B15" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128474510</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128474395</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128474957</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>128475218</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128475242</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128474420</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>128474707</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128474935</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128474886</v>
       </c>
       <c r="B26" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35905-2025 artfynd.xlsx
+++ b/artfynd/A 35905-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>128474972</v>
       </c>
       <c r="B11" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>128474772</v>
       </c>
       <c r="B12" t="n">
-        <v>56294</v>
+        <v>56297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128475036</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128475015</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128475088</v>
       </c>
       <c r="B15" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128474510</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128474395</v>
       </c>
       <c r="B17" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128474743</v>
       </c>
       <c r="B18" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128474957</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128474296</v>
       </c>
       <c r="B20" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>128475218</v>
       </c>
       <c r="B21" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128475242</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128474420</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>128474707</v>
       </c>
       <c r="B24" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128474935</v>
       </c>
       <c r="B25" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128474886</v>
       </c>
       <c r="B26" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
